--- a/resources/templates/karaba/power_of_attorney.xlsx
+++ b/resources/templates/karaba/power_of_attorney.xlsx
@@ -158,9 +158,7 @@
     <t>인천광역시 중구 인중로 178 정우빌딩 303호</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">120111-0922270</t>
-    </r>
+    <t>120111-1058941</t>
   </si>
   <si>
     <r>
@@ -817,7 +815,7 @@
     <col min="16" max="16" width="1.375" customWidth="true" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16145" customHeight="1" ht="55.5" s="21" customFormat="1">
+    <row r="1" spans="1:16" customHeight="1" ht="55.5" s="21" customFormat="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
           <r>
@@ -827,7 +825,7 @@
       </c>
       <c r="O1" s="7"/>
     </row>
-    <row r="2" spans="1:16145" customHeight="1" ht="36" s="21" customFormat="1">
+    <row r="2" spans="1:16" customHeight="1" ht="36" s="21" customFormat="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -843,7 +841,7 @@
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
     </row>
-    <row r="3" spans="1:16145" customHeight="1" ht="36.75" s="21" customFormat="1">
+    <row r="3" spans="1:16" customHeight="1" ht="36.75" s="21" customFormat="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
           <r>
@@ -852,7 +850,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:16145" customHeight="1" ht="54.75" s="21" customFormat="1">
+    <row r="4" spans="1:16" customHeight="1" ht="54.75" s="21" customFormat="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
           <r>
@@ -893,7 +891,7 @@
       <c r="M4" s="22"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:16145" customHeight="1" ht="54.75" s="21" customFormat="1">
+    <row r="5" spans="1:16" customHeight="1" ht="54.75" s="21" customFormat="1">
       <c r="A5" s="20" t="inlineStr">
         <is>
           <r>
@@ -929,7 +927,7 @@
       <c r="M5" s="22"/>
       <c r="N5" s="23"/>
     </row>
-    <row r="6" spans="1:16145" customHeight="1" ht="16.5" s="21" customFormat="1">
+    <row r="6" spans="1:16" customHeight="1" ht="16.5" s="21" customFormat="1">
       <c r="A6" s="3"/>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -945,7 +943,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:16145" customHeight="1" ht="34.5" s="21" customFormat="1">
+    <row r="7" spans="1:16" customHeight="1" ht="34.5" s="21" customFormat="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <r>
@@ -954,7 +952,7 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:16145" customHeight="1" ht="34.5" s="21" customFormat="1">
+    <row r="8" spans="1:16" customHeight="1" ht="34.5" s="21" customFormat="1">
       <c r="A8" s="12" t="inlineStr">
         <is>
           <r>
@@ -963,7 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:16145" customHeight="1" ht="34.5" s="21" customFormat="1">
+    <row r="9" spans="1:16" customHeight="1" ht="34.5" s="21" customFormat="1">
       <c r="A9" s="12" t="inlineStr">
         <is>
           <r>
@@ -972,7 +970,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:16145" customHeight="1" ht="18" s="21" customFormat="1">
+    <row r="10" spans="1:16" customHeight="1" ht="18" s="21" customFormat="1">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="5"/>
@@ -988,7 +986,7 @@
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
     </row>
-    <row r="11" spans="1:16145" customHeight="1" ht="34.5" s="21" customFormat="1">
+    <row r="11" spans="1:16" customHeight="1" ht="34.5" s="21" customFormat="1">
       <c r="A11" s="24" t="inlineStr">
         <is>
           <r>
@@ -1015,7 +1013,7 @@
       <c r="M11" s="24"/>
       <c r="N11" s="24"/>
     </row>
-    <row r="12" spans="1:16145" customHeight="1" ht="12.75" s="21" customFormat="1">
+    <row r="12" spans="1:16" customHeight="1" ht="12.75" s="21" customFormat="1">
       <c r="A12" s="5"/>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -1031,7 +1029,7 @@
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:16145" customHeight="1" ht="37.5" s="21" customFormat="1">
+    <row r="13" spans="1:16" customHeight="1" ht="37.5" s="21" customFormat="1">
       <c r="A13" s="14" t="inlineStr">
         <is>
           <r>
@@ -1040,7 +1038,7 @@
         </is>
       </c>
     </row>
-    <row r="14" spans="1:16145" customHeight="1" ht="37.5" s="21" customFormat="1">
+    <row r="14" spans="1:16" customHeight="1" ht="37.5" s="21" customFormat="1">
       <c r="A14" s="14" t="inlineStr">
         <is>
           <r>
@@ -1049,7 +1047,7 @@
         </is>
       </c>
     </row>
-    <row r="15" spans="1:16145" customHeight="1" ht="37.5" s="21" customFormat="1">
+    <row r="15" spans="1:16" customHeight="1" ht="37.5" s="21" customFormat="1">
       <c r="A15" s="14" t="inlineStr">
         <is>
           <r>
@@ -1058,7 +1056,7 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="1:16145" customHeight="1" ht="12.75" s="21" customFormat="1">
+    <row r="16" spans="1:16" customHeight="1" ht="12.75" s="21" customFormat="1">
       <c r="A16" s="5"/>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -1074,7 +1072,7 @@
       <c r="M16" s="5"/>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="1:16145" customHeight="1" ht="40.5" s="21" customFormat="1">
+    <row r="17" spans="1:16" customHeight="1" ht="40.5" s="21" customFormat="1">
       <c r="A17" s="10" t="inlineStr">
         <is>
           <r>
@@ -1083,7 +1081,7 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="18" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A18" s="25" t="inlineStr">
         <is>
           <r>
@@ -1112,7 +1110,7 @@
       <c r="M18" s="27"/>
       <c r="N18" s="26"/>
     </row>
-    <row r="19" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="19" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A19" s="25" t="inlineStr">
         <is>
           <r>
@@ -1140,7 +1138,7 @@
       <c r="M19" s="27"/>
       <c r="N19" s="26"/>
     </row>
-    <row r="20" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="20" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
           <r>
@@ -1181,10 +1179,10 @@
       <c r="M20" s="27"/>
       <c r="N20" s="26"/>
     </row>
-    <row r="21" spans="1:16145" customHeight="1" ht="20.25" s="21" customFormat="1">
+    <row r="21" spans="1:16" customHeight="1" ht="20.25" s="21" customFormat="1">
       <c r="A21" s="16"/>
     </row>
-    <row r="22" spans="1:16145" customHeight="1" ht="41.25" s="21" customFormat="1">
+    <row r="22" spans="1:16" customHeight="1" ht="41.25" s="21" customFormat="1">
       <c r="A22" s="10" t="inlineStr">
         <is>
           <r>
@@ -1193,7 +1191,7 @@
         </is>
       </c>
     </row>
-    <row r="23" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="23" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
           <r>
@@ -1218,7 +1216,7 @@
       <c r="M23" s="27"/>
       <c r="N23" s="26"/>
     </row>
-    <row r="24" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="24" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
           <r>
@@ -1242,7 +1240,7 @@
       <c r="M24" s="27"/>
       <c r="N24" s="26"/>
     </row>
-    <row r="25" spans="1:16145" customHeight="1" ht="44.25" s="21" customFormat="1">
+    <row r="25" spans="1:16" customHeight="1" ht="44.25" s="21" customFormat="1">
       <c r="A25" s="25" t="inlineStr">
         <is>
           <r>
@@ -1252,12 +1250,8 @@
         </is>
       </c>
       <c r="B25" s="26"/>
-      <c r="C25" s="25" t="inlineStr">
-        <is>
-          <r>
-            <t xml:space="preserve">120111-0922270</t>
-          </r>
-        </is>
+      <c r="C25" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="D25" s="27"/>
       <c r="E25" s="27"/>
@@ -1283,10 +1277,10 @@
       <c r="M25" s="27"/>
       <c r="N25" s="26"/>
     </row>
-    <row r="26" spans="1:16145" customHeight="1" ht="20.25" s="21" customFormat="1">
+    <row r="26" spans="1:16" customHeight="1" ht="20.25" s="21" customFormat="1">
       <c r="A26" s="16"/>
     </row>
-    <row r="27" spans="1:16145" customHeight="1" ht="20.25" s="21" customFormat="1">
+    <row r="27" spans="1:16" customHeight="1" ht="20.25" s="21" customFormat="1">
       <c r="A27" s="18" t="inlineStr">
         <is>
           <r>
@@ -1295,7 +1289,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:16145" customHeight="1" ht="20.25" s="21" customFormat="1">
+    <row r="28" spans="1:16" customHeight="1" ht="20.25" s="21" customFormat="1">
       <c r="A28" s="16"/>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -1311,7 +1305,7 @@
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
     </row>
-    <row r="29" spans="1:16145" customHeight="1" ht="50.25" s="21" customFormat="1">
+    <row r="29" spans="1:16" customHeight="1" ht="50.25" s="21" customFormat="1">
       <c r="A29" s="17" t="inlineStr">
         <is>
           <r>
